--- a/product_selector_out/STM32L4x1 - diff.xlsx
+++ b/product_selector_out/STM32L4x1 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -79,6 +94,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -597,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="18">
@@ -655,18 +673,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -678,62 +700,70 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -742,21 +772,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -765,76 +795,88 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -848,7 +890,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -857,7 +899,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -871,7 +913,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -880,90 +922,102 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -972,21 +1026,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -995,94 +1049,102 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1091,21 +1153,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1114,117 +1176,125 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1233,94 +1303,102 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1329,21 +1407,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1352,76 +1430,88 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1435,7 +1525,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1444,7 +1534,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1458,7 +1548,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1467,121 +1557,125 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1590,76 +1684,88 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1677,7 +1783,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -1686,7 +1792,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1700,7 +1806,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1709,7 +1815,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1723,7 +1829,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1732,78 +1838,1853 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>STM32L451RE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32L451RE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32L451RE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32L471QG</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32L471QG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32L471QG</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32L471QG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32L471QG</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L431CC</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L431RB</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L431RB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L431RB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L431RB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32L431RB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L431RB</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L451CE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L451CE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L451CE</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L451CE</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32L451CE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32L471QE</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32L471QE</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32L471QE</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32L471QE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32L471QE</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>STM32L431VC</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E67"/>
+  <autoFilter ref="A18:E136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x1 - diff.xlsx
+++ b/product_selector_out/STM32L4x1 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -86,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,7 +91,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -565,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -635,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1272</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="18">
@@ -1770,22 +1764,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1797,13 +1787,13 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -1815,23 +1805,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1856,9 +1850,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1869,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1883,9 +1877,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1897,22 +1891,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1914,13 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -1942,23 +1932,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1983,9 +1977,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2002,7 +1996,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2010,9 +2004,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2024,22 +2018,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2051,13 +2041,13 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2069,23 +2059,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2110,9 +2104,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2123,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2137,9 +2131,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2151,22 +2145,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2177,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10||11</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2191,9 +2185,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2204,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2218,9 +2212,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2232,22 +2226,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>10||11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2259,68 +2249,72 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2331,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2345,9 +2339,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2359,22 +2353,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2386,95 +2376,99 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2486,22 +2480,18 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2513,29 +2503,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2545,63 +2531,71 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2613,22 +2607,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2640,29 +2630,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2672,7 +2658,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2680,55 +2666,63 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2740,22 +2734,18 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2767,29 +2757,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2799,63 +2785,71 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2867,17 +2861,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -2894,17 +2888,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -2921,17 +2915,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -2948,22 +2942,18 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>10||11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2975,117 +2965,117 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>10, 11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3102,29 +3092,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3134,24 +3120,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3161,51 +3147,51 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3228,7 +3214,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3251,7 +3237,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3261,12 +3247,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -3278,7 +3264,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3288,12 +3274,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -3305,7 +3291,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3315,12 +3301,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -3332,7 +3318,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3355,7 +3341,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3378,7 +3364,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3405,7 +3391,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3432,7 +3418,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3459,45 +3445,41 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3506,185 +3488,8 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32L431KB</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E136"/>
+  <autoFilter ref="A18:E129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x1 - diff.xlsx
+++ b/product_selector_out/STM32L4x1 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1344</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -789,27 +789,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -834,9 +830,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -853,7 +849,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -861,9 +857,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -875,18 +871,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -898,13 +898,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -916,54 +916,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -980,7 +972,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -988,9 +980,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1002,18 +994,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1025,99 +1021,91 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1129,18 +1117,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1144,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1180,7 +1176,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1188,81 +1184,73 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1279,25 +1267,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1307,24 +1299,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1334,62 +1326,58 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1401,18 +1389,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1424,7 +1412,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1451,7 +1439,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1478,7 +1466,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1505,7 +1493,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1528,7 +1516,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1551,34 +1539,30 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1588,24 +1572,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1615,58 +1599,62 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -1678,61 +1666,53 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1742,197 +1722,201 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1942,89 +1926,81 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2036,30 +2012,34 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2077,16 +2057,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2096,7 +2076,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2104,297 +2084,289 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>10||11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>10, 11</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2404,7 +2376,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2412,104 +2384,108 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2521,61 +2497,53 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2585,197 +2553,201 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2785,7 +2757,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2793,185 +2765,177 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>10||11</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -2983,61 +2947,53 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3047,197 +3003,201 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3247,7 +3207,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3255,104 +3215,108 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3364,61 +3328,53 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3428,7 +3384,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3436,60 +3392,587 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>STM32L431VC</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr">
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E129"/>
+  <autoFilter ref="A18:E150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>